--- a/data/trans_orig/P41E_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023</t>
+          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36093</t>
+          <t>35672</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56069</t>
+          <t>55317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56707</t>
+          <t>58273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78235</t>
+          <t>78308</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97766</t>
+          <t>98671</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126911</t>
+          <t>126834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17175</t>
+          <t>17059</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32135</t>
+          <t>31255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21165</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36093</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41924</t>
+          <t>42292</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63496</t>
+          <t>62996</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18394</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>33985</t>
+          <t>34293</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48556</t>
+          <t>48776</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68429</t>
+          <t>68150</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70354</t>
+          <t>71809</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>97315</t>
+          <t>96017</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37183</t>
+          <t>36216</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59602</t>
+          <t>59021</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47908</t>
+          <t>48869</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67290</t>
+          <t>68497</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90501</t>
+          <t>92594</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120363</t>
+          <t>121021</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,59%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>82142</t>
+          <t>83294</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111722</t>
+          <t>111203</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51837</t>
+          <t>52704</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73665</t>
+          <t>74429</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>142899</t>
+          <t>143896</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180065</t>
+          <t>182922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27377</t>
+          <t>26096</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>77128</t>
+          <t>76548</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>61696</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70273</t>
+          <t>68792</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130787</t>
+          <t>130558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48440</t>
+          <t>49595</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14086</t>
+          <t>14139</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38833</t>
+          <t>39292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>40659</t>
+          <t>39808</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81953</t>
+          <t>82933</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>43258</t>
+          <t>47775</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>127244</t>
+          <t>128142</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>41448</t>
+          <t>40448</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110409</t>
+          <t>109955</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>122687</t>
+          <t>122022</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>228774</t>
+          <t>225415</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160627</t>
+          <t>149323</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>392352</t>
+          <t>395250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139041</t>
+          <t>152207</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>348184</t>
+          <t>349514</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>413593</t>
+          <t>382540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>722462</t>
+          <t>717861</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>547473</t>
+          <t>539996</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>911366</t>
+          <t>935061</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>530519</t>
+          <t>528378</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>848818</t>
+          <t>838724</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1088792</t>
+          <t>1098030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1589206</t>
+          <t>1631606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>72,69%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13009</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5936</t>
+          <t>5752</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15520</t>
+          <t>15190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11071</t>
+          <t>11083</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>23903</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>14346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>2419</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8514</t>
+          <t>8787</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24553</t>
+          <t>23479</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43545</t>
+          <t>43611</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>19076</t>
+          <t>18667</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>33261</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>46265</t>
+          <t>45837</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70141</t>
+          <t>70465</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>99474</t>
+          <t>100045</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>134407</t>
+          <t>132735</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94374</t>
+          <t>94217</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>122214</t>
+          <t>122057</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,22%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>202351</t>
+          <t>203246</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>248807</t>
+          <t>248448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163239</t>
+          <t>163073</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>201215</t>
+          <t>203093</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>155870</t>
+          <t>158085</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186367</t>
+          <t>186571</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>331948</t>
+          <t>328905</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>382316</t>
+          <t>377899</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67570</t>
+          <t>65636</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132574</t>
+          <t>134292</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84129</t>
+          <t>78817</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146954</t>
+          <t>147494</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>176842</t>
+          <t>172674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>268166</t>
+          <t>268247</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>38498</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>82834</t>
+          <t>84770</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38652</t>
+          <t>38933</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76681</t>
+          <t>76242</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97340</t>
+          <t>94711</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>154755</t>
+          <t>154484</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>94795</t>
+          <t>97223</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>188362</t>
+          <t>188793</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>110451</t>
+          <t>108984</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>197709</t>
+          <t>197187</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>244204</t>
+          <t>239801</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>373210</t>
+          <t>371102</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>285913</t>
+          <t>291663</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>557338</t>
+          <t>557044</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>275789</t>
+          <t>297309</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>511893</t>
+          <t>512667</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>693412</t>
+          <t>684948</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1039521</t>
+          <t>1035964</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>820009</t>
+          <t>818923</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1262123</t>
+          <t>1252115</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>754586</t>
+          <t>754345</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1166263</t>
+          <t>1154868</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1599251</t>
+          <t>1610660</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2206112</t>
+          <t>2215700</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,7%</t>
+          <t>47,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41E_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44302</t>
+          <t>48143</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>35672</t>
+          <t>39103</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55317</t>
+          <t>59556</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>67249</t>
+          <t>73634</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58273</t>
+          <t>62527</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78308</t>
+          <t>86472</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>111551</t>
+          <t>121777</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98671</t>
+          <t>107854</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>126834</t>
+          <t>138842</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23877</t>
+          <t>25695</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17059</t>
+          <t>18483</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>31255</t>
+          <t>34559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27860</t>
+          <t>31413</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>23808</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>40960</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>51737</t>
+          <t>57108</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>42292</t>
+          <t>46899</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62996</t>
+          <t>69237</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24838</t>
+          <t>29839</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17661</t>
+          <t>21379</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>34293</t>
+          <t>40268</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58451</t>
+          <t>63300</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>48776</t>
+          <t>52786</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68150</t>
+          <t>74021</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>83289</t>
+          <t>93139</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71809</t>
+          <t>80232</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96017</t>
+          <t>108380</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>54165</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36216</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59021</t>
+          <t>65802</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>57598</t>
+          <t>64016</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48869</t>
+          <t>54711</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68497</t>
+          <t>76412</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>105243</t>
+          <t>118181</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92594</t>
+          <t>103255</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121021</t>
+          <t>136177</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>98180</t>
+          <t>106862</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83294</t>
+          <t>91571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>111203</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>46,56%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>63118</t>
+          <t>67582</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52704</t>
+          <t>56747</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>74429</t>
+          <t>80071</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>161298</t>
+          <t>174444</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>143896</t>
+          <t>154712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>182922</t>
+          <t>194541</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>238842</t>
+          <t>264703</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>238842</t>
+          <t>264703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>238842</t>
+          <t>264703</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>274276</t>
+          <t>299946</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>274276</t>
+          <t>299946</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>274276</t>
+          <t>299946</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>513118</t>
+          <t>564649</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>513118</t>
+          <t>564649</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>513118</t>
+          <t>564649</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>55908</t>
+          <t>58769</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26096</t>
+          <t>45771</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76548</t>
+          <t>73431</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>45420</t>
+          <t>49485</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24024</t>
+          <t>39032</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61696</t>
+          <t>61522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>101328</t>
+          <t>108254</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68792</t>
+          <t>90981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130558</t>
+          <t>125788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34749</t>
+          <t>37008</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16839</t>
+          <t>27379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>49595</t>
+          <t>48472</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27144</t>
+          <t>29589</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14139</t>
+          <t>21568</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39292</t>
+          <t>41267</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>61892</t>
+          <t>66597</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>39808</t>
+          <t>53779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>82933</t>
+          <t>81913</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>95399</t>
+          <t>105412</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>47775</t>
+          <t>86231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128142</t>
+          <t>124721</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>83733</t>
+          <t>90716</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>40448</t>
+          <t>75292</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>109955</t>
+          <t>106287</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>179132</t>
+          <t>196128</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>122022</t>
+          <t>173415</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>225415</t>
+          <t>225054</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,43%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>302363</t>
+          <t>335774</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149323</t>
+          <t>305680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>395250</t>
+          <t>368696</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>36,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>273863</t>
+          <t>312267</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>152207</t>
+          <t>289249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>349514</t>
+          <t>339199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>32,6%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>576226</t>
+          <t>648041</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>382540</t>
+          <t>608105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>717861</t>
+          <t>689734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>35,05%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>683916</t>
+          <t>473169</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>539996</t>
+          <t>439538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>935061</t>
+          <t>506258</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>641999</t>
+          <t>475937</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>528378</t>
+          <t>448386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>838724</t>
+          <t>502112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1325915</t>
+          <t>949106</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1098030</t>
+          <t>906101</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1631606</t>
+          <t>990353</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>50,32%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1172334</t>
+          <t>1010131</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1172334</t>
+          <t>1010131</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1172334</t>
+          <t>1010131</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1072159</t>
+          <t>957995</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1072159</t>
+          <t>957995</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1072159</t>
+          <t>957995</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2244493</t>
+          <t>1968126</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2244493</t>
+          <t>1968126</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2244493</t>
+          <t>1968126</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7126</t>
+          <t>7175</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3725</t>
+          <t>4019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>12448</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9602</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5752</t>
+          <t>6045</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>16394</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>16727</t>
+          <t>17483</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11083</t>
+          <t>11497</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23903</t>
+          <t>24948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8410</t>
+          <t>9637</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4701</t>
+          <t>5112</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14346</t>
+          <t>16330</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2419</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10640</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,17 +2272,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>15378</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8787</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>22763</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>32192</t>
+          <t>33021</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>23479</t>
+          <t>24961</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43611</t>
+          <t>44784</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>25319</t>
+          <t>26901</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>18667</t>
+          <t>20188</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>33261</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>57511</t>
+          <t>59922</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>48303</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>70465</t>
+          <t>73304</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>116623</t>
+          <t>133220</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>100045</t>
+          <t>115191</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>132735</t>
+          <t>153054</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>107801</t>
+          <t>125822</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>94217</t>
+          <t>111545</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>122057</t>
+          <t>143270</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>39,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>224424</t>
+          <t>259042</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>203246</t>
+          <t>233633</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>248448</t>
+          <t>282949</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>38,13%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>182432</t>
+          <t>200183</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>163073</t>
+          <t>178808</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>203093</t>
+          <t>221632</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>46,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>171634</t>
+          <t>190123</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>158085</t>
+          <t>173278</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186571</t>
+          <t>205934</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>57,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>354065</t>
+          <t>390307</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>328905</t>
+          <t>364497</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>377899</t>
+          <t>419784</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,56%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>346783</t>
+          <t>383236</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>346783</t>
+          <t>383236</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>346783</t>
+          <t>383236</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>319771</t>
+          <t>358895</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>319771</t>
+          <t>358895</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>319771</t>
+          <t>358895</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>666554</t>
+          <t>742131</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>666554</t>
+          <t>742131</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>666554</t>
+          <t>742131</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>107335</t>
+          <t>114086</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>65636</t>
+          <t>97612</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>134292</t>
+          <t>134878</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>122271</t>
+          <t>133427</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78817</t>
+          <t>116807</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>147494</t>
+          <t>151472</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>229606</t>
+          <t>247513</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>172674</t>
+          <t>223168</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>268247</t>
+          <t>274037</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>67036</t>
+          <t>72339</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>59987</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84770</t>
+          <t>88481</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>60419</t>
+          <t>66744</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>38933</t>
+          <t>54486</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>76242</t>
+          <t>80371</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>127455</t>
+          <t>139083</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94711</t>
+          <t>120413</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>154484</t>
+          <t>159808</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>152429</t>
+          <t>168271</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>97223</t>
+          <t>144055</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>188793</t>
+          <t>192598</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>167503</t>
+          <t>180917</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>108984</t>
+          <t>159083</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>197187</t>
+          <t>201382</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>319932</t>
+          <t>349189</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>239801</t>
+          <t>319294</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>371102</t>
+          <t>380630</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>466632</t>
+          <t>523159</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>291663</t>
+          <t>487120</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>557044</t>
+          <t>559823</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>439263</t>
+          <t>502105</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>297309</t>
+          <t>468986</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>512667</t>
+          <t>532423</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>32,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>905894</t>
+          <t>1025264</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>684948</t>
+          <t>975053</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1035964</t>
+          <t>1076333</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>32,87%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>964527</t>
+          <t>780215</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>818923</t>
+          <t>738231</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1252115</t>
+          <t>825363</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>54,87%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>876751</t>
+          <t>733641</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>754345</t>
+          <t>700011</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1154868</t>
+          <t>768327</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>45,38%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>47,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1841278</t>
+          <t>1513856</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1610660</t>
+          <t>1459703</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2215700</t>
+          <t>1571161</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>47,98%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1757958</t>
+          <t>1658071</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1757958</t>
+          <t>1658071</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1757958</t>
+          <t>1658071</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1666207</t>
+          <t>1616835</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1666207</t>
+          <t>1616835</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1666207</t>
+          <t>1616835</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3424165</t>
+          <t>3274906</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3424165</t>
+          <t>3274906</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3424165</t>
+          <t>3274906</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">

--- a/data/trans_orig/P41E_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41E_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si con respecto al último año sus relaciones sexuales han sido satisfactorias para ambas partes en 2023 (tasa de respuesta: 69,32%)</t>
+          <t>Población según su nivel de acuerdo sobre la satisfacción de sus relaciones sexuales por ambas partes en el último mes en 2023 (tasa de respuesta: 69,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
